--- a/stories/arbres/TREE-REL-006.xlsx
+++ b/stories/arbres/TREE-REL-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la fenêtre, Inès voit Tom dans le jardin d'à côté. Elle a envie de jouer. Papa ouvre un peu la fenêtre. Maman prépare le goûter. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1511,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est dans le jardin. Inès a envie d'inviter. C'est Tom. Le seau sonne, tout léger. Inès s'approche, sans courir. Maman n'est pas loin. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On a envie de jouer ensemble. Que dit-on ? Avec Tom.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Inès retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi les cubes, après Tom. Un crayon sent le bois. Inès range un peu autour des cubes. Elle respire. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2583,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2555,7 +2612,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint une pomme, après Tom et les cubes. La tasse est encore tiède. On dit merci. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. Le soleil est encore là.</t>
+          <t>Inès rejoint une pomme, après Tom et les cubes. La tasse est encore tiède. On dit merci. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2693,6 +2750,13 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Tom et les cubes. La tasse est encore tiède. On dit merci. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2879,7 +2948,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un yaourt, après Tom et les cubes. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On gardu geste.</t>
+          <t>Inès rejoint un yaourt, après Tom et les cubes. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3017,6 +3086,12 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Tom et les cubes. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3254,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3203,7 +3283,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un morceau de pain, après Tom et les cubes. Une abeille bourdonne loin. On attend un petit moment. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+          <t>Inès rejoint un morceau de pain, après Tom et les cubes. Une abeille bourdonne loin. On attend un petit moment. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3341,6 +3421,12 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Tom et les cubes. Une abeille bourdonne loin. On attend un petit moment. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3589,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3756,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le livre, après Tom. Un gravier roule sous une semelle. On parle du livre. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3947,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3976,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint une pomme, après Tom et le livre. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On respire.</t>
+          <t>Inès rejoint une pomme, après Tom et le livre. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4114,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Tom et le livre. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4199,7 +4311,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un yaourt, après Tom et le livre. La fenêtre tremble un tout petit peu. On sourit un peu. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
+          <t>Inès rejoint un yaourt, après Tom et le livre. La fenêtre tremble un tout petit peu. On sourit un peu. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4337,6 +4449,12 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Tom et le livre. La fenêtre tremble un tout petit peu. On sourit un peu. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4617,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4646,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un morceau de pain, après Tom et le livre. Ça sent le savon de maman. On boit une gorgée d'eau. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. Le jeu peut recommencer.</t>
+          <t>Inès rejoint un morceau de pain, après Tom et le livre. Ça sent le savon de maman. On boit une gorgée d'eau. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4784,13 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Tom et le livre. Ça sent le savon de maman. On boit une gorgée d'eau. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4953,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5120,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi la dînette, après Tom. Une vague chuchote. On parle de la dînette. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5311,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5195,7 +5340,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint une pomme, après Tom et la dînette. Un pigeon roucoule. On essuie une miette. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On se serre un peu.</t>
+          <t>Inès rejoint une pomme, après Tom et la dînette. Un pigeon roucoule. On essuie une miette. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5333,6 +5478,12 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Tom et la dînette. Un pigeon roucoule. On essuie une miette. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5519,7 +5675,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un yaourt, après Tom et la dînette. La cuillère tinte. On referme un livre. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On rentre.</t>
+          <t>Inès rejoint un yaourt, après Tom et la dînette. La cuillère tinte. On referme un livre. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5657,6 +5813,12 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Tom et la dînette. La cuillère tinte. On referme un livre. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5981,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5843,7 +6010,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un morceau de pain, après Tom et la dînette. Le ballon est un peu poudreux. On pose un jouet à sa place. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. La journée continue, tout doux.</t>
+          <t>Inès rejoint un morceau de pain, après Tom et la dînette. Le ballon est un peu poudreux. On pose un jouet à sa place. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5981,6 +6148,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Tom et la dînette. Le ballon est un peu poudreux. On pose un jouet à sa place. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6317,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6484,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa passe avec un livre. Inès a envie d'inviter. Inès s'occupe de Léa. Une goutte tombe dans l'évier. Papa sourit. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6665,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On a envie de jouer ensemble. Que dit-on ? Avec Léa.</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6838,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Inès répète le mot. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7029,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6997,6 +7196,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi les cubes, après Léa. La laine du doudou est douce. Les cubes est là. Inès pose les mains à vue, loin de l'autre. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7387,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7207,7 +7416,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint une pomme, après Léa et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
+          <t>Inès rejoint une pomme, après Léa et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7345,6 +7554,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Léa et les cubes. Une goutte de pluie sèche déjà. On marche tout doucement. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7722,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7531,7 +7751,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un yaourt, après Léa et les cubes. Le banc est tiède. On se tait une seconde. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. Le soleil est encore là.</t>
+          <t>Inès rejoint un yaourt, après Léa et les cubes. Le banc est tiède. On se tait une seconde. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7669,6 +7889,13 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Léa et les cubes. Le banc est tiède. On se tait une seconde. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8058,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7855,7 +8087,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un morceau de pain, après Léa et les cubes. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On gardu geste.</t>
+          <t>Inès rejoint un morceau de pain, après Léa et les cubes. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -7993,6 +8225,12 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Léa et les cubes. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8393,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8560,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le livre, après Léa. Le seau sonne, tout léger. On parle du livre. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8751,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8527,7 +8780,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint une pomme, après Léa et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+          <t>Inès rejoint une pomme, après Léa et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8665,6 +8918,12 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Léa et le livre. Une feuille tourne et tombe. On s'assoit près de l'adulte. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9086,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8851,7 +9115,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un yaourt, après Léa et le livre. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On respire.</t>
+          <t>Inès rejoint un yaourt, après Léa et le livre. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -8989,6 +9253,12 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Léa et le livre. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9175,7 +9450,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un morceau de pain, après Léa et le livre. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
+          <t>Inès rejoint un morceau de pain, après Léa et le livre. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9313,6 +9588,12 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Léa et le livre. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9756,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9923,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi la dînette, après Léa. Ça sent l'herbe coupée. Inès s'installe avec la dînette. Papa reste à portée de voix. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10114,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9847,7 +10143,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint une pomme, après Léa et la dînette. Une plume vole. On range les chaussures. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. Le jeu peut recommencer.</t>
+          <t>Inès rejoint une pomme, après Léa et la dînette. Une plume vole. On range les chaussures. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9985,6 +10281,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Léa et la dînette. Une plume vole. On range les chaussures. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10450,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10171,7 +10479,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un yaourt, après Léa et la dînette. Le pain croustille. On met le doudou près de soi. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On se serre un peu.</t>
+          <t>Inès rejoint un yaourt, après Léa et la dînette. Le pain croustille. On met le doudou près de soi. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10309,6 +10617,12 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Léa et la dînette. Le pain croustille. On met le doudou près de soi. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10785,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10495,7 +10814,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint un morceau de pain, après Léa et la dînette. La laine du doudou est douce. On écoute le cœur, tout doux. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Papa dit : je t'ai entendu. Maman aussi. On rentre.</t>
+          <t>Inès rejoint un morceau de pain, après Léa et la dînette. La laine du doudou est douce. On écoute le cœur, tout doux. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10633,6 +10952,12 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Léa et la dînette. La laine du doudou est douce. On écoute le cœur, tout doux. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.
+papa|Je t'ai entendu. Maman aussi. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11120,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11287,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami pousse un vélo. Inès a envie d'inviter. Voilà Sami. Le train souffle au loin. Inès pose les pieds par terre, près de papa. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On a envie de jouer ensemble. Que dit-on ? Avec Sami.</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Inès pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11487,6 +11832,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11511,7 +11861,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Inès a choisi les cubes, après Sami. Le savon sent la fleur. Inès touche les cubes tout doucement. Papa dit : je suis là. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+          <t>Inès a choisi les cubes, après Sami. Le savon sent la fleur. Inès touche les cubes tout doucement. Je suis là. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11649,6 +11999,13 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi les cubes, après Sami. Le savon sent la fleur. Inès touche les cubes tout doucement.
+papa|Je suis là.
+narrateur|Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12192,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12359,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Sami et les cubes. Un galet est lisse dans la main. On secoue les mains, loin. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse une pomme à sa place. Inès est près de papa. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12526,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12693,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Sami et les cubes. Le train souffle au loin. On pose le sac. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un yaourt à sa place. Inès est près de papa. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12860,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13027,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Sami et les cubes. Une vache meugle, loin. On dit le mot de l'émotion. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un morceau de pain à sa place. Inès est près de papa. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13194,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13361,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le livre, après Sami. Ça sent l'herbe coupée. On parle du livre. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13552,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13317,6 +13719,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Sami et le livre. Un grillon chante, tout petit. On invite d'une petite voix. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse une pomme à sa place. Inès est près de papa. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13886,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14053,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Sami et le livre. Le bois de la table est lisse. On attend la réponse. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un yaourt à sa place. Inès est près de papa. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14220,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14387,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Sami et le livre. Une goutte tombe dans l'évier. On propose une autre idée. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un morceau de pain à sa place. Inès est près de papa. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14554,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14289,6 +14721,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi la dînette, après Sami. Un crayon sent le bois. On parle de la dînette. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14912,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15079,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint une pomme, après Sami et la dînette. Le toboggan est un peu froid. On va vers papa ou maman. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse une pomme à sa place. Inès est près de papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15246,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15413,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un yaourt, après Sami et la dînette. La clochette de la porte tinte. On dit stop, tout clair. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un yaourt à sa place. Inès est près de papa. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15580,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15747,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint un morceau de pain, après Sami et la dînette. Ça sent le thym du jardin. On s'éloigne d'un pas. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un morceau de pain à sa place. Inès est près de papa. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15914,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15482,6 +15954,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-006.xlsx
+++ b/stories/arbres/TREE-REL-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Près de la fenêtre, Inès voit Tom dans le jardin d'à côté. Elle a envie de jouer. Papa ouvre un peu la fenêtre. Maman prépare le goûter. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Tom est dans le jardin. Inès a envie d'inviter. C'est Tom. Le seau sonne, tout léger. Inès s'approche, sans courir. Maman n'est pas loin. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|On a envie de jouer ensemble. Que dit-on ? Avec Tom.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Oui. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Inès retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Inès a choisi les cubes, après Tom. Un crayon sent le bois. Inès range un peu autour des cubes. Elle respire. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
 narrateur|Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3092,6 +3107,7 @@
 papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3259,6 +3275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3444,7 @@
 papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3780,7 @@
           <t>narrateur|Inès a choisi le livre, après Tom. Un gravier roule sous une semelle. On parle du livre. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
 papa|Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4455,6 +4478,7 @@
 papa|Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4622,6 +4646,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4791,6 +4816,7 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4958,6 +4984,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5125,6 +5152,7 @@
           <t>narrateur|Inès a choisi la dînette, après Tom. Une vague chuchote. On parle de la dînette. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5316,6 +5344,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
 papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5819,6 +5850,7 @@
 papa|Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5986,6 +6018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6155,6 +6188,7 @@
 narrateur|La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6322,6 +6356,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6489,6 +6524,7 @@
           <t>narrateur|Léa passe avec un livre. Inès a envie d'inviter. Inès s'occupe de Léa. Une goutte tombe dans l'évier. Papa sourit. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6672,6 +6708,7 @@
           <t>narrateur|On a envie de jouer ensemble. Que dit-on ? Avec Léa.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6843,6 +6880,7 @@
           <t>narrateur|Oui. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Inès répète le mot. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7034,6 +7072,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7201,6 +7240,7 @@
           <t>narrateur|Inès a choisi les cubes, après Léa. La laine du doudou est douce. Les cubes est là. Inès pose les mains à vue, loin de l'autre. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7392,6 +7432,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7560,6 +7601,7 @@
 papa|Je t'ai entendu. Maman aussi. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7727,6 +7769,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7896,6 +7939,7 @@
 narrateur|Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8063,6 +8107,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8231,6 +8276,7 @@
 papa|Je t'ai entendu. Maman aussi. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8398,6 +8444,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8565,6 +8612,7 @@
           <t>narrateur|Inès a choisi le livre, après Léa. Le seau sonne, tout léger. On parle du livre. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8756,6 +8804,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8924,6 +8973,7 @@
 papa|Je t'ai entendu. Maman aussi. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9091,6 +9141,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
 papa|Je t'ai entendu. Maman aussi. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9594,6 +9647,7 @@
 papa|Je t'ai entendu. Maman aussi. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9761,6 +9815,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9928,6 +9983,7 @@
           <t>narrateur|Inès a choisi la dînette, après Léa. Ça sent l'herbe coupée. Inès s'installe avec la dînette. Papa reste à portée de voix. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10119,6 +10175,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10288,6 +10345,7 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10455,6 +10513,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10623,6 +10682,7 @@
 papa|Je t'ai entendu. Maman aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10790,6 +10850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10958,6 +11019,7 @@
 papa|Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11125,6 +11187,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
           <t>narrateur|Sami pousse un vélo. Inès a envie d'inviter. Voilà Sami. Le train souffle au loin. Inès pose les pieds par terre, près de papa. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|On a envie de jouer ensemble. Que dit-on ? Avec Sami.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|Oui. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. Inès pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11837,6 +11903,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12006,6 +12073,7 @@
 narrateur|Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12197,6 +12265,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12364,6 +12433,7 @@
           <t>narrateur|Inès rejoint une pomme, après Sami et les cubes. Un galet est lisse dans la main. On secoue les mains, loin. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse une pomme à sa place. Inès est près de papa. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12531,6 +12601,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12698,6 +12769,7 @@
           <t>narrateur|Inès rejoint un yaourt, après Sami et les cubes. Le train souffle au loin. On pose le sac. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un yaourt à sa place. Inès est près de papa. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12865,6 +12937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13032,6 +13105,7 @@
           <t>narrateur|Inès rejoint un morceau de pain, après Sami et les cubes. Une vache meugle, loin. On dit le mot de l'émotion. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un morceau de pain à sa place. Inès est près de papa. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13199,6 +13273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13366,6 +13441,7 @@
           <t>narrateur|Inès a choisi le livre, après Sami. Ça sent l'herbe coupée. On parle du livre. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13557,6 +13633,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13724,6 +13801,7 @@
           <t>narrateur|Inès rejoint une pomme, après Sami et le livre. Un grillon chante, tout petit. On invite d'une petite voix. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse une pomme à sa place. Inès est près de papa. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13891,6 +13969,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14058,6 +14137,7 @@
           <t>narrateur|Inès rejoint un yaourt, après Sami et le livre. Le bois de la table est lisse. On attend la réponse. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un yaourt à sa place. Inès est près de papa. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14225,6 +14305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14392,6 +14473,7 @@
           <t>narrateur|Inès rejoint un morceau de pain, après Sami et le livre. Une goutte tombe dans l'évier. On propose une autre idée. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un morceau de pain à sa place. Inès est près de papa. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14559,6 +14641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14726,6 +14809,7 @@
           <t>narrateur|Inès a choisi la dînette, après Sami. Un crayon sent le bois. On parle de la dînette. Inès écoute jusqu'au bout. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14917,6 +15001,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15084,6 +15169,7 @@
           <t>narrateur|Inès rejoint une pomme, après Sami et la dînette. Le toboggan est un peu froid. On va vers papa ou maman. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse une pomme à sa place. Inès est près de papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15251,6 +15337,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15418,6 +15505,7 @@
           <t>narrateur|Inès rejoint un yaourt, après Sami et la dînette. La clochette de la porte tinte. On dit stop, tout clair. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un yaourt à sa place. Inès est près de papa. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15585,6 +15673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15752,6 +15841,7 @@
           <t>narrateur|Inès rejoint un morceau de pain, après Sami et la dînette. Ça sent le thym du jardin. On s'éloigne d'un pas. Inès peut inviter : tu veux jouer avec nous ? Elle peut accepter un non. Un non, c'est possible. Papa est là. On laisse un morceau de pain à sa place. Inès est près de papa. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15919,6 +16009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15937,7 +16028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15961,6 +16052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15975,7 +16080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16162,6 +16267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
